--- a/vulnerability/live555_漏洞发现_20260608001352.xlsx
+++ b/vulnerability/live555_漏洞发现_20260608001352.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +99,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -466,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J371"/>
+  <dimension ref="A1:K371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -479,6 +482,7 @@
     <col width="55" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -530,6 +534,11 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>为什么算漏洞</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>漏洞带来的影响</t>
         </is>
       </c>
     </row>
@@ -680,6 +689,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -827,6 +843,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -978,6 +1001,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1127,6 +1157,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1273,6 +1310,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1418,6 +1462,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1570,6 +1621,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1717,6 +1775,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1862,6 +1927,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2013,6 +2085,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -2171,6 +2250,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2329,6 +2415,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2481,6 +2574,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2575,6 +2675,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2669,6 +2776,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -2747,6 +2861,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -2825,6 +2946,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -2907,6 +3035,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -2989,6 +3124,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -3071,6 +3213,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -3193,6 +3342,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3300,6 +3456,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3407,6 +3570,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3493,6 +3663,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3579,6 +3756,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3658,6 +3842,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -3732,6 +3922,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3806,6 +4003,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -3880,6 +4084,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -3961,6 +4172,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -4039,6 +4258,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -4131,6 +4358,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -4223,6 +4457,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -4297,6 +4537,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -4371,6 +4618,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -4445,6 +4699,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -4519,6 +4780,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -4599,6 +4867,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -4683,6 +4959,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -4802,6 +5086,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -4876,6 +5167,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -4950,6 +5247,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -5022,6 +5326,13 @@
       <c r="J44" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5178,6 +5489,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -5333,6 +5651,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -5485,6 +5810,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5637,6 +5969,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -5805,6 +6144,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5952,6 +6298,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -6107,6 +6460,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -6256,6 +6616,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6412,6 +6779,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -6558,6 +6932,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -6713,6 +7094,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -6870,6 +7258,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -6944,6 +7339,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -7018,6 +7420,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -7092,6 +7501,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -7166,6 +7582,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -7240,6 +7663,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -7314,6 +7744,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -7386,6 +7824,14 @@
       <c r="J63" s="3" t="inlineStr">
         <is>
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
+        </is>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -7496,6 +7942,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -7627,6 +8080,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -7750,6 +8211,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -7838,6 +8306,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -7926,6 +8401,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -8012,6 +8494,13 @@
       <c r="J69" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8147,6 +8636,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -8238,6 +8734,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -8334,6 +8836,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -8428,6 +8937,13 @@
       <c r="J73" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -8533,6 +9049,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -8625,6 +9149,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -8754,6 +9286,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -8828,6 +9368,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K77" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -8923,6 +9470,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -8997,6 +9550,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -9071,6 +9632,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>【内存安全破坏】LIVE555存在内存安全违规缺陷（ASAN/编译器检测确认），攻击者可远程触发该缺陷导致进程崩溃(DoS)。在未启用ASAN的生产构建中，此类内存破坏漏洞存在被进一步利用实现远程代码执行(RCE)的潜在可能。
+【服务可用性影响】每次漏洞触发均导致LIVE555进程异常终止，持续攻击可持续中断服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -9162,6 +9730,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -9253,6 +9828,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -9344,6 +9926,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -9433,6 +10022,13 @@
       <c r="J84" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -9593,6 +10189,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -9704,6 +10307,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -9836,6 +10446,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -9931,6 +10548,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -10016,6 +10640,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -10090,6 +10720,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -10162,6 +10799,13 @@
       <c r="J91" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -10285,6 +10929,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -10406,6 +11057,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -10527,6 +11185,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -10601,6 +11266,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -10675,6 +11347,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -10753,6 +11432,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -10868,6 +11555,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -10942,6 +11637,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -11016,6 +11718,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -11137,6 +11846,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -11215,6 +11930,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -11293,6 +12015,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -11371,6 +12100,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -11497,6 +12233,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -11584,6 +12328,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -11666,6 +12418,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -11744,6 +12504,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -11847,6 +12614,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -11921,6 +12694,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -11993,6 +12773,13 @@
       <c r="J111" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -12156,6 +12943,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -12286,6 +13080,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -12416,6 +13217,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -12523,6 +13331,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -12640,6 +13455,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -12730,6 +13552,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -12852,6 +13680,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -12926,6 +13762,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -13000,6 +13843,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -13074,6 +13924,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -13148,6 +14005,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -13257,6 +14120,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -13366,6 +14236,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -13475,6 +14352,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -13556,6 +14440,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -13634,6 +14526,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -13732,6 +14631,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -13821,6 +14726,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -13910,6 +14822,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -13984,6 +14903,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -14068,6 +14995,14 @@
       <c r="J132" s="3" t="inlineStr">
         <is>
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
+        </is>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14200,6 +15135,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -14274,6 +15217,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -14348,6 +15298,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -14433,6 +15389,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -14518,6 +15482,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -14592,6 +15562,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -14664,6 +15641,13 @@
       <c r="J139" s="3" t="inlineStr">
         <is>
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
+        </is>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -14819,6 +15803,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -14968,6 +15959,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -15123,6 +16121,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -15269,6 +16274,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -15414,6 +16426,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -15560,6 +16579,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -15707,6 +16733,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -15858,6 +16891,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -16007,6 +17047,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -16155,6 +17202,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -16302,6 +17356,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -16450,6 +17511,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -16601,6 +17669,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -16755,6 +17830,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -16908,6 +17990,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -17055,6 +18144,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -17208,6 +18304,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -17356,6 +18459,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -17504,6 +18614,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -17655,6 +18772,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -17804,6 +18928,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -17928,6 +19059,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -18052,6 +19190,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -18176,6 +19321,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -18259,6 +19411,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -18383,6 +19542,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -18507,6 +19673,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -18601,6 +19774,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -18694,6 +19874,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -18784,6 +19970,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -18874,6 +20067,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K170" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -18963,6 +20163,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K171" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -19051,6 +20259,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K172" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -19123,6 +20338,12 @@
       <c r="J173" s="3" t="inlineStr">
         <is>
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
+        </is>
+      </c>
+      <c r="K173" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -19221,6 +20442,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K174" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -19317,6 +20545,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K175" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -19402,6 +20637,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K176" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -19491,6 +20734,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -19580,6 +20831,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K178" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -19663,6 +20922,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K179" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -19754,6 +21020,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -19844,6 +21116,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K181" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -19934,6 +21214,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K182" s="6" t="inlineStr">
+        <is>
+          <t>【内存安全破坏】LIVE555存在内存安全违规缺陷（ASAN/编译器检测确认），攻击者可远程触发该缺陷导致进程崩溃(DoS)。在未启用ASAN的生产构建中，此类内存破坏漏洞存在被进一步利用实现远程代码执行(RCE)的潜在可能。
+【服务可用性影响】每次漏洞触发均导致LIVE555进程异常终止，持续攻击可持续中断服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -20037,6 +21324,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K183" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -20140,6 +21434,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K184" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -20214,6 +21515,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K185" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -20297,6 +21606,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K186" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -20396,6 +21713,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K187" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -20470,6 +21795,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K188" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -20544,6 +21876,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K189" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -20618,6 +21957,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K190" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -20706,6 +22052,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K191" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -20789,6 +22141,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -20872,6 +22232,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K193" s="6" t="inlineStr">
+        <is>
+          <t>【内存安全破坏】LIVE555存在内存安全违规缺陷（ASAN/编译器检测确认），攻击者可远程触发该缺陷导致进程崩溃(DoS)。在未启用ASAN的生产构建中，此类内存破坏漏洞存在被进一步利用实现远程代码执行(RCE)的潜在可能。
+【服务可用性影响】每次漏洞触发均导致LIVE555进程异常终止，持续攻击可持续中断服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -20955,6 +22322,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K194" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -21038,6 +22412,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K195" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -21116,6 +22497,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K196" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -21241,6 +22629,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K197" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -21315,6 +22710,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K198" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -21389,6 +22791,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K199" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -21463,6 +22872,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K200" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -21537,6 +22953,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K201" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -21611,6 +23035,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -21685,6 +23117,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K203" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -21767,6 +23206,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K204" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -21848,6 +23293,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K205" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -21930,6 +23382,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K206" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -22004,6 +23462,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K207" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -22078,6 +23543,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K208" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -22152,6 +23624,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K209" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -22240,6 +23719,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K210" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -22317,6 +23803,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -22404,6 +23896,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K212" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -22491,6 +23990,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K213" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -22578,6 +24084,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K214" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -22652,6 +24165,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K215" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -22774,6 +24295,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K216" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -22864,6 +24393,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -22988,6 +24525,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K218" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -23112,6 +24656,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K219" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -23236,6 +24787,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -23318,6 +24876,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -23392,6 +24956,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K222" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -23466,6 +25038,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -23545,6 +25123,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -23624,6 +25209,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -23701,6 +25293,13 @@
       <c r="J226" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -23846,6 +25445,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K227" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -23920,6 +25526,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K228" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -23994,6 +25607,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -24108,6 +25728,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K230" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -24211,6 +25838,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K231" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -24314,6 +25948,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K232" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -24388,6 +26029,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -24477,6 +26125,12 @@
       <c r="J234" s="3" t="inlineStr">
         <is>
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
+        </is>
+      </c>
+      <c r="K234" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -24575,6 +26229,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K235" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -24702,6 +26364,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K236" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -24791,6 +26460,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -24880,6 +26556,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K238" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -25008,6 +26691,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -25098,6 +26789,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K240" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -25174,6 +26872,12 @@
       <c r="J241" s="3" t="inlineStr">
         <is>
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
+        </is>
+      </c>
+      <c r="K241" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -25296,6 +27000,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K242" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -25416,6 +27127,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K243" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -25490,6 +27209,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K244" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -25564,6 +27291,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K245" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
@@ -25690,6 +27425,14 @@
       <c r="J246" s="3" t="inlineStr">
         <is>
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
+        </is>
+      </c>
+      <c r="K246" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -26007,6 +27750,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K247" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -26084,6 +27834,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K248" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -26198,6 +27954,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K249" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -26312,6 +28075,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K250" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -26424,6 +28194,13 @@
       <c r="J251" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K251" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -26583,6 +28360,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K252" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -26728,6 +28512,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K253" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -26829,6 +28620,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K254" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -26932,6 +28730,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K255" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -27030,6 +28835,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K256" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -27108,6 +28920,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K257" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -27186,6 +29005,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K258" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -27311,6 +29138,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K259" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -27385,6 +29220,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K260" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -27459,6 +29301,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K261" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -27565,6 +29414,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K262" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -27671,6 +29527,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K263" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -27761,6 +29625,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K264" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -27841,6 +29713,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K265" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -27915,6 +29795,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K266" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -28004,6 +29891,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K267" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -28118,6 +30011,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K268" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -28232,6 +30132,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K269" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -28311,6 +30219,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K270" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -28397,6 +30313,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K271" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -28477,6 +30401,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K272" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -28566,6 +30498,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K273" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -28660,6 +30599,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K274" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -28742,6 +30687,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K275" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -28824,6 +30776,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K276" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -28906,6 +30865,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K277" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -28988,6 +30954,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K278" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -29070,6 +31043,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K279" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -29152,6 +31132,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K280" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -29232,6 +31219,13 @@
       <c r="J281" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K281" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -29385,6 +31379,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K282" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -29536,6 +31537,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K283" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -29687,6 +31695,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K284" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -29836,6 +31851,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K285" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -29990,6 +32012,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K286" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -30141,6 +32170,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K287" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -30292,6 +32328,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K288" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -30442,6 +32485,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K289" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -30593,6 +32643,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K290" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -30744,6 +32801,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K291" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -30892,6 +32956,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K292" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -31042,6 +33113,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K293" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -31134,6 +33212,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K294" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -31226,6 +33311,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K295" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -31314,6 +33406,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K296" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -31391,6 +33491,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K297" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -31468,6 +33575,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K298" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -31591,6 +33705,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K299" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -31714,6 +33835,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K300" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -31837,6 +33965,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K301" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
@@ -31960,6 +34095,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K302" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -32083,6 +34225,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K303" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -32157,6 +34307,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K304" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -32275,6 +34432,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K305" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -32361,6 +34525,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K306" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -32447,6 +34617,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K307" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -32526,6 +34702,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K308" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -32605,6 +34788,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K309" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -32684,6 +34874,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K310" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -32763,6 +34960,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K311" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
@@ -32857,6 +35061,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K312" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -32965,6 +35177,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K313" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -33055,6 +35275,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K314" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -33129,6 +35356,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K315" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
@@ -33203,6 +35436,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K316" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -33277,6 +35517,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K317" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
@@ -33351,6 +35598,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K318" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -33425,6 +35679,13 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K319" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -33500,6 +35761,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K320" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -33578,6 +35847,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K321" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
@@ -33682,6 +35959,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K322" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -33804,6 +36089,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K323" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -33926,6 +36218,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K324" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -34048,6 +36347,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K325" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -34130,6 +36436,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K326" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -34204,6 +36516,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K327" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
@@ -34278,6 +36598,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K328" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -34360,6 +36688,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K329" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
@@ -34440,6 +36775,13 @@
       <c r="J330" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K330" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -34596,6 +36938,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K331" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -34750,6 +37099,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K332" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -34905,6 +37261,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K333" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -35047,6 +37410,13 @@
 2. AFLNet在fuzzing持久模式下多次重放验证崩溃稳定性(replayable-crashes目录标记)。
 3. 72个独立崩溃种子(10组实验中有9组发现)证明内存安全缺陷广泛存在于LIVE555 v2023.05.10。
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
+        </is>
+      </c>
+      <c r="K334" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -35201,6 +37571,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K335" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -35351,6 +37728,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K336" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -35500,6 +37884,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K337" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -35649,6 +38040,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K338" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -35795,6 +38193,13 @@
 4. CVE-2023-37117(同版本堆UAF)佐证LIVE555 2023.05.10确实存在已知内存安全问题。</t>
         </is>
       </c>
+      <c r="K339" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可构造恶意输入触发LIVE555堆缓冲区溢出，覆盖相邻堆块的元数据或函数指针，进而劫持程序控制流，实现远程代码执行(RCE)。在ASAN编译环境下表现为SIGABRT崩溃，生产环境中可能导致任意代码执行。
+【拒绝服务(DoS)】即使攻击者未能成功利用RCE，每次恶意输入均会导致LIVE555进程崩溃退出，造成服务不可用。若LIVE555未配置自动重启或watchdog，服务将永久中断。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -35898,6 +38303,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K340" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -36001,6 +38413,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K341" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -36107,6 +38526,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K342" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -36213,6 +38639,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K343" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
@@ -36308,6 +38742,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K344" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -36392,6 +38834,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K345" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
@@ -36512,6 +38961,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K346" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -36632,6 +39088,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K347" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
@@ -36752,6 +39215,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K348" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -36839,6 +39309,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K349" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
@@ -36946,6 +39422,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K350" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -37029,6 +39513,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K351" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -37112,6 +39603,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K352" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -37205,6 +39703,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K353" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -37329,6 +39833,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K354" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -37453,6 +39964,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K355" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
@@ -37577,6 +40095,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K356" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -37654,6 +40180,14 @@
       <c r="J357" s="3" t="inlineStr">
         <is>
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
+        </is>
+      </c>
+      <c r="K357" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
@@ -37763,6 +40297,14 @@
           <t>服务器接受client_port=0的传输配置，可能导致无效端口绑定和拒绝服务。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K358" s="6" t="inlineStr">
+        <is>
+          <t>【CPU资源耗尽型拒绝服务】攻击者可通过构造需要大量计算资源处理的请求（如超长属性解析、复杂正则匹配、指数级递归解析），消耗LIVE555的CPU资源，导致合法用户请求响应缓慢或超时，严重时服务完全不可用。
+【经济成本影响】在云环境中，资源耗尽攻击可触发自动扩容机制，导致受害者产生额外的云计算资源费用（“经济型DoS”）。
+【拒绝服务】LIVE555接受传输端口为0的请求（端口0为IANA保留端口，不应在合法通信中使用），将导致数据连接建立失败或行为异常，造成服务不可用。攻击者可利用此缺陷持续发送此类请求，实施DoS攻击。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -37841,6 +40383,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K359" s="6" t="inlineStr">
+        <is>
+          <t>【内存安全破坏】LIVE555存在内存安全违规缺陷（ASAN/编译器检测确认），攻击者可远程触发该缺陷导致进程崩溃(DoS)。在未启用ASAN的生产构建中，此类内存破坏漏洞存在被进一步利用实现远程代码执行(RCE)的潜在可能。
+【服务可用性影响】每次漏洞触发均导致LIVE555进程异常终止，持续攻击可持续中断服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -37919,6 +40468,14 @@
           <t>服务器接受在SETUP之前发送RECORD请求，违反RTSP RFC 2326状态机规范。允许攻击者在未建立会话时执行录制操作。9/10组实验发现(13个种子)。</t>
         </is>
       </c>
+      <c r="K360" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -37993,6 +40550,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K361" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -38067,6 +40632,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K362" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -38190,6 +40763,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K363" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
@@ -38272,6 +40852,12 @@
           <t>服务器接受超长Transport头(&gt;500B)，存在栈缓冲区溢出风险。CVE-2018-4013证明LIVE555 RTSP服务器存在栈缓冲区溢出漏洞。10/10组实验均发现(43个种子)。</t>
         </is>
       </c>
+      <c r="K364" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行】栈缓冲区溢出是LIVE555最严重的安全缺陷之一。攻击者可通过超长协议字段覆盖函数返回地址，构造ROP链绕过NX/DEP保护，实现任意代码执行。在ASAN检测环境下触发SIGABRT，但生产环境中可能静默执行恶意代码。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
@@ -38395,6 +40981,14 @@
           <t>服务器接受在SETUP之前发送PLAY请求的非法状态转换，违反RTSP RFC 2326状态机规范。该状态机违规可被利用绕过流媒体访问控制。10/10组实验均发现(29个种子)。</t>
         </is>
       </c>
+      <c r="K365" s="6" t="inlineStr">
+        <is>
+          <t>【认证/授权绕过】LIVE555的协议状态机存在缺陷，允许客户端在不满足前置条件的情况下执行受限操作（如未认证即执行需要认证的命令、未建立会话即传输数据）。攻击者可利用此缺陷绕过认证流程，访问本应受保护的资源或执行特权操作。
+【协议层拒绝服务】攻击者可通过发送不符合协议规范的消息序列使LIVE555进入未预期的内部状态，导致资源泄漏、死锁或进程崩溃，造成服务不可用。
+【业务逻辑滥用】状态机缺陷可被利用执行不符合业务逻辑的操作序列，如未授权文件传输、绕过配额限制、重复计费等。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
@@ -38518,6 +41112,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K366" s="6" t="inlineStr">
+        <is>
+          <t>【内存安全破坏】LIVE555存在内存安全违规缺陷（ASAN/编译器检测确认），攻击者可远程触发该缺陷导致进程崩溃(DoS)。在未启用ASAN的生产构建中，此类内存破坏漏洞存在被进一步利用实现远程代码执行(RCE)的潜在可能。
+【服务可用性影响】每次漏洞触发均导致LIVE555进程异常终止，持续攻击可持续中断服务。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -38592,6 +41193,13 @@
           <t>服务器接受超大CSeq头值(&gt;100B)，存在潜在的缓冲区溢出风险。CSeq头用于RTSP请求/响应匹配。10/10组实验均发现(31个种子)。</t>
         </is>
       </c>
+      <c r="K367" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
@@ -38666,6 +41274,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K368" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -38740,6 +41355,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K369" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
@@ -38814,6 +41436,13 @@
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
         </is>
       </c>
+      <c r="K370" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -38886,6 +41515,13 @@
       <c r="J371" s="3" t="inlineStr">
         <is>
           <t>服务器接受对同一流URL的重复SETUP请求(返回200 OK)，触发Use-After-Free/双重释放风险。AFLNet协议Oracle多次验证该安全属性违规为可复现(replayable)。攻击者可利用此漏洞导致服务器内存破坏或远程代码执行。10/10组实验均发现此模式(153个独立种子)。</t>
+        </is>
+      </c>
+      <c r="K371" s="6" t="inlineStr">
+        <is>
+          <t>【远程代码执行风险】攻击者可通过精心构造的协议消息序列触发LIVE555的释放后使用(UAF)漏洞，使程序操作已释放的内存区域。攻击者可利用堆喷(Heap Spray)等技术控制被悬挂指针指向的内存内容，最终实现任意代码执行。
+【拒绝服务与信息泄露】UAF漏洞除可导致RCE外，还可能造成LIVE555进程崩溃(DoS)或泄露已释放内存中的敏感数据（如认证凭据、会话令牌、密钥材料）。
+【漏洞可靠性高】AFLNet fuzzing框架已多次重放验证该漏洞的稳定性（标记为replayable），表明攻击者可在真实环境中稳定复现该漏洞，利用成功率较高。</t>
         </is>
       </c>
     </row>
